--- a/outputs/tables/posrri_results.xlsx
+++ b/outputs/tables/posrri_results.xlsx
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Plan would work in a Tier 2 spill</t>
+          <t>The plan would work in a Tier 2 spill</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Confidence in the notification chain</t>
+          <t>The notification chain is dependable</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Plan would work in a Tier 2 spill</t>
+          <t>The plan would work in a Tier 2 spill</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Confidence in the notification chain</t>
+          <t>The notification chain is dependable</t>
         </is>
       </c>
       <c r="C6" t="n">

--- a/outputs/tables/posrri_results.xlsx
+++ b/outputs/tables/posrri_results.xlsx
@@ -27,6 +27,8 @@
     <sheet name="17_survey_frequencies" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="18_survey_text" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="19_survey_alpha_items" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="20_survey_org_groups" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="21_survey_org_audit" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,7 +718,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8152</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -731,11 +733,26 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.02</v>
+        <v>2.971</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>highest q4, lowest q9</t>
+          <t>highest q4, lowest q10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Organisation groups represented</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4 free-text -&gt; Other, 7 left blank</t>
         </is>
       </c>
     </row>
@@ -8501,10 +8518,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7866228513106404</v>
+        <v>0.9044109595053951</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -8516,16 +8533,16 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -8546,10 +8563,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8992059989632124</v>
+        <v>0.8656718518596066</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
@@ -8564,13 +8581,13 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -8591,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9035079029052513</v>
+        <v>0.8980704940286691</v>
       </c>
       <c r="G4" t="n">
         <v>4</v>
@@ -8615,7 +8632,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>56.00000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -8639,7 +8656,7 @@
         <v>3.26</v>
       </c>
       <c r="F5" t="n">
-        <v>1.026386568382061</v>
+        <v>0.9435062700547638</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
@@ -8657,10 +8674,10 @@
         <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -8681,10 +8698,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9981615754036243</v>
+        <v>0.9216223495022464</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -8693,19 +8710,19 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>4</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5</v>
-      </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -8726,10 +8743,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9278018789216868</v>
+        <v>0.9930369826847296</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -8744,13 +8761,13 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -8771,13 +8788,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7583548251421142</v>
+        <v>0.8628382211738</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -8792,10 +8809,10 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -9066,16 +9083,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>30.23255813953488</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="G8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9098,16 +9115,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>34.88372093023256</v>
+        <v>29.54545454545455</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -9130,16 +9147,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>30.23255813953488</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="G10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -9162,16 +9179,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>4.651162790697675</v>
+        <v>11.36363636363636</v>
       </c>
       <c r="G11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -9190,14 +9207,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Less than 2 years</t>
+          <t>Less than 5 years</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>50</v>
@@ -9222,14 +9239,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2-5 years</t>
+          <t>5 to 10 years</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
         <v>50</v>
@@ -9254,14 +9271,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6-10 years</t>
+          <t>11 to 20 years</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G14" t="n">
         <v>50</v>
@@ -9286,14 +9303,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>More than 10 years</t>
+          <t>More than 20 years</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
         <v>50</v>
@@ -9429,49 +9446,49 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Unclear lines of authority (10); Equipment is not maintained (8); No dedicated budget (8)</t>
+          <t>Unclear lines of authority (10); Plan is out of date (8); Too few trained staff (7)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>q12</t>
+          <t>q12_raw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Most valuable single change (free text)</t>
+          <t>Organisation type (as answered)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Run a full-scale annual exercise (11); Appoint a permanent on-scene commander (10); Publish the plan to all terminals (8)</t>
+          <t>Chattogram Port Authority (10); Other government agency (Coast Guard, DoE, Department of Shipping, etc.) (7); Bangladesh Navy (5)</t>
         </is>
       </c>
     </row>
@@ -9483,24 +9500,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Organisation (free text)</t>
+          <t>Further comments (free text)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Terminal operator (10); Fisheries department (8); Coast guard (8)</t>
+          <t>Plan should be public (10); More boom stock is essential (9); Exercises need to involve the terminals (7)</t>
         </is>
       </c>
     </row>
@@ -11216,16 +11233,16 @@
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7866228513106404</v>
+        <v>0.9044109595053951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6746395812294175</v>
+        <v>0.6216826970535809</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7734506742370474</v>
+        <v>0.774449948162654</v>
       </c>
     </row>
     <row r="3">
@@ -11243,16 +11260,16 @@
         <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8992059989632124</v>
+        <v>0.8656718518596066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.510368406187348</v>
+        <v>0.5151268771854871</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7981333333333333</v>
+        <v>0.7929340145668007</v>
       </c>
     </row>
     <row r="4">
@@ -11270,16 +11287,16 @@
         <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9035079029052513</v>
+        <v>0.8980704940286691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5588007800662219</v>
+        <v>0.440534434887423</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7898923937423695</v>
+        <v>0.8054347826086957</v>
       </c>
     </row>
     <row r="5">
@@ -11300,13 +11317,13 @@
         <v>3.26</v>
       </c>
       <c r="E5" t="n">
-        <v>1.026386568382061</v>
+        <v>0.9435062700547638</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6120143818795296</v>
+        <v>0.572811816089183</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7804175314369429</v>
+        <v>0.7829329057014404</v>
       </c>
     </row>
     <row r="6">
@@ -11324,16 +11341,16 @@
         <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9981615754036243</v>
+        <v>0.9216223495022464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5894146360065474</v>
+        <v>0.486112918120393</v>
       </c>
       <c r="G6" t="n">
-        <v>0.784620895522388</v>
+        <v>0.7981390766536218</v>
       </c>
     </row>
     <row r="7">
@@ -11351,16 +11368,16 @@
         <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9278018789216868</v>
+        <v>0.9930369826847296</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5316176181231257</v>
+        <v>0.6571707868871767</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7946992864424056</v>
+        <v>0.7666221628838452</v>
       </c>
     </row>
     <row r="8">
@@ -11378,16 +11395,674 @@
         <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7583548251421142</v>
+        <v>0.8628382211738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4164860157789656</v>
+        <v>0.5485168077401786</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8116054951814639</v>
+        <v>0.7874752366277791</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>q12_group</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>group_short</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_of_valid</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>n_valid</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>n_missing</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chattogram Port Authority</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23.25581395348837</v>
+      </c>
+      <c r="E2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bangladesh Navy</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.6046511627907</v>
+      </c>
+      <c r="E3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Other government agency (Coast Guard, DoE, Department of Shipping, etc.)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Govt agency</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20.93023255813954</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shipping agent</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Shipping agent</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.302325581395349</v>
+      </c>
+      <c r="E5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shipping line or vessel operator</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Shipping line</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13.95348837209302</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Master or ship's officer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Master/officer</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.651162790697675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Terminal, jetty or oil company</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Terminal/oil co.</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>43</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9.302325581395349</v>
+      </c>
+      <c r="E9" t="n">
+        <v>43</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>q12_raw</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>q12_group</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>group_short</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chattogram Port Authority</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chattogram Port Authority</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bangladesh Navy</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bangladesh Navy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BANGLADESH NAVY</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bangladesh Navy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Other government agency (Coast Guard, DoE, Department of Shipping, etc.)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Other government agency (Coast Guard, DoE, Department of Shipping, etc.)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Govt agency</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OTHER GOVERNMENT AGENCY (COAST GUARD, DOE, DEPARTMENT OF SHIPPING, ETC.)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other government agency (Coast Guard, DoE, Department of Shipping, etc.)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Govt agency</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Shipping agent</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Shipping agent</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Shipping agent</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SHIPPING AGENT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Shipping agent</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Shipping agent</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shipping line or vessel operator</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Shipping line or vessel operator</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shipping line</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SHIPPING LINE OR VESSEL OPERATOR</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Shipping line or vessel operator</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Shipping line</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Master or ship's officer</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Master or ship's officer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Master/officer</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>listed option</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>(missing)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(missing)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>blank -&gt; missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>University researcher</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>free text -&gt; Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Customs broker</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>free text -&gt; Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fisheries cooperative</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>free text -&gt; Other</t>
+        </is>
       </c>
     </row>
   </sheetData>
